--- a/R_Codes/DataSummary/All_Prokaryotes/Sample_name/All_Prokaryotes_Summary_Class_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/All_Prokaryotes/Sample_name/All_Prokaryotes_Summary_Class_by_Sample_name.xlsx
@@ -904,10 +904,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>16.6994495871233</v>
+        <v>16.69721476412</v>
       </c>
       <c r="D2" t="n">
-        <v>0.544021954552858</v>
+        <v>0.546555498622618</v>
       </c>
     </row>
     <row r="3">
@@ -918,10 +918,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>10.7628959810556</v>
+        <v>10.7593837024178</v>
       </c>
       <c r="D3" t="n">
-        <v>0.407087596772065</v>
+        <v>0.406835428428408</v>
       </c>
     </row>
     <row r="4">
@@ -932,10 +932,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>9.46591936237537</v>
+        <v>9.46865957347609</v>
       </c>
       <c r="D4" t="n">
-        <v>0.191183292818498</v>
+        <v>0.191252945879903</v>
       </c>
     </row>
     <row r="5">
@@ -946,10 +946,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>7.06646519850493</v>
+        <v>7.06664624046094</v>
       </c>
       <c r="D5" t="n">
-        <v>0.13584723651329</v>
+        <v>0.135842348000212</v>
       </c>
     </row>
     <row r="6">
@@ -960,10 +960,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>7.01538098706899</v>
+        <v>7.01467567205716</v>
       </c>
       <c r="D6" t="n">
-        <v>0.199360754590101</v>
+        <v>0.199253355768674</v>
       </c>
     </row>
     <row r="7">
@@ -974,10 +974,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.74468851215764</v>
+        <v>4.74851307529336</v>
       </c>
       <c r="D7" t="n">
-        <v>0.706461728295311</v>
+        <v>0.707275444521839</v>
       </c>
     </row>
     <row r="8">
@@ -988,10 +988,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.35072596514309</v>
+        <v>4.35102958031309</v>
       </c>
       <c r="D8" t="n">
-        <v>0.104430812322395</v>
+        <v>0.104400926922469</v>
       </c>
     </row>
     <row r="9">
@@ -1002,10 +1002,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>4.29487637892786</v>
+        <v>4.29983825234804</v>
       </c>
       <c r="D9" t="n">
-        <v>0.641426529304867</v>
+        <v>0.64241403583849</v>
       </c>
     </row>
     <row r="10">
@@ -1016,10 +1016,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.28347834235104</v>
+        <v>3.27249146125443</v>
       </c>
       <c r="D10" t="n">
-        <v>0.79915348640349</v>
+        <v>0.871921977785763</v>
       </c>
     </row>
     <row r="11">
@@ -1030,10 +1030,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>2.4269888027386</v>
+        <v>2.42656791040234</v>
       </c>
       <c r="D11" t="n">
-        <v>0.283271304850249</v>
+        <v>0.283201164940256</v>
       </c>
     </row>
     <row r="12">
@@ -1044,10 +1044,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>2.08902184937749</v>
+        <v>2.0891099450425</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0706745150316027</v>
+        <v>0.0706662999116921</v>
       </c>
     </row>
     <row r="13">
@@ -1058,10 +1058,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>1.93758540635085</v>
+        <v>1.9386018524867</v>
       </c>
       <c r="D13" t="n">
-        <v>0.218533707382644</v>
+        <v>0.21865273225635</v>
       </c>
     </row>
     <row r="14">
@@ -1072,10 +1072,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>1.65181412581786</v>
+        <v>1.65213774608583</v>
       </c>
       <c r="D14" t="n">
-        <v>0.249286546400501</v>
+        <v>0.249357480884307</v>
       </c>
     </row>
     <row r="15">
@@ -1086,10 +1086,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1.49213500624218</v>
+        <v>1.4919442619445</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0305929966125898</v>
+        <v>0.0305772187518557</v>
       </c>
     </row>
     <row r="16">
@@ -1100,10 +1100,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.31561220963714</v>
+        <v>1.31536584951405</v>
       </c>
       <c r="D16" t="n">
-        <v>0.224020070752134</v>
+        <v>0.223995295658811</v>
       </c>
     </row>
     <row r="17">
@@ -1114,10 +1114,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.23235412870257</v>
+        <v>1.233089743625</v>
       </c>
       <c r="D17" t="n">
-        <v>0.042983074143062</v>
+        <v>0.043030021347402</v>
       </c>
     </row>
     <row r="18">
@@ -1128,10 +1128,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.12006945516452</v>
+        <v>1.12041017444424</v>
       </c>
       <c r="D18" t="n">
-        <v>0.135803475180083</v>
+        <v>0.135837812532254</v>
       </c>
     </row>
     <row r="19">
@@ -1142,10 +1142,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.07937609823973</v>
+        <v>1.07866942197931</v>
       </c>
       <c r="D19" t="n">
-        <v>0.158533684085452</v>
+        <v>0.158425901133258</v>
       </c>
     </row>
     <row r="20">
@@ -1156,10 +1156,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>1.07124779500138</v>
+        <v>1.07204551066076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0617081216960804</v>
+        <v>0.0617764407603995</v>
       </c>
     </row>
     <row r="21">
@@ -1170,10 +1170,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>1.02167265406125</v>
+        <v>1.02224220013233</v>
       </c>
       <c r="D21" t="n">
-        <v>0.224034569670493</v>
+        <v>0.224069778626305</v>
       </c>
     </row>
     <row r="22">
@@ -1184,10 +1184,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.991190646365845</v>
+        <v>0.991214815160951</v>
       </c>
       <c r="D22" t="n">
-        <v>0.137170354779316</v>
+        <v>0.137193208020609</v>
       </c>
     </row>
     <row r="23">
@@ -1198,10 +1198,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.975106580758331</v>
+        <v>0.975265896868867</v>
       </c>
       <c r="D23" t="n">
-        <v>0.117586369526141</v>
+        <v>0.117601905592498</v>
       </c>
     </row>
     <row r="24">
@@ -1212,10 +1212,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.942019245174214</v>
+        <v>0.94151232214195</v>
       </c>
       <c r="D24" t="n">
-        <v>0.370427466384496</v>
+        <v>0.370227991956522</v>
       </c>
     </row>
     <row r="25">
@@ -1226,10 +1226,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.729901630188444</v>
+        <v>0.730483140491789</v>
       </c>
       <c r="D25" t="n">
-        <v>0.114986922000628</v>
+        <v>0.115145981293474</v>
       </c>
     </row>
     <row r="26">
@@ -1240,10 +1240,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.679860756418902</v>
+        <v>0.680139963718148</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0256500189960307</v>
+        <v>0.0256569108303947</v>
       </c>
     </row>
     <row r="27">
@@ -1254,10 +1254,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.660980969615619</v>
+        <v>0.660999046429082</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0927532732636472</v>
+        <v>0.0927583565588167</v>
       </c>
     </row>
     <row r="28">
@@ -1268,10 +1268,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.655040031421386</v>
+        <v>0.65488059499132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0499614906311154</v>
+        <v>0.0499389194021385</v>
       </c>
     </row>
     <row r="29">
@@ -1282,10 +1282,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.624604224265717</v>
+        <v>0.624704056866684</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0118696757506593</v>
+        <v>0.0118778493907195</v>
       </c>
     </row>
     <row r="30">
@@ -1296,10 +1296,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.556352932022276</v>
+        <v>0.556400267744252</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0755179985551829</v>
+        <v>0.0754916195891344</v>
       </c>
     </row>
     <row r="31">
@@ -1310,10 +1310,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.538901045976734</v>
+        <v>0.538824251893525</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0171736367669633</v>
+        <v>0.0171725141860427</v>
       </c>
     </row>
     <row r="32">
@@ -1324,10 +1324,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.486845887529014</v>
+        <v>0.486943081222954</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0326665349579771</v>
+        <v>0.0326674794619765</v>
       </c>
     </row>
     <row r="33">
@@ -1338,10 +1338,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.448384575788155</v>
+        <v>0.448457161030202</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0311103611774359</v>
+        <v>0.0311052922869941</v>
       </c>
     </row>
     <row r="34">
@@ -1352,10 +1352,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.445925941969867</v>
+        <v>0.445990783436791</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0235316965200081</v>
+        <v>0.0235442551494637</v>
       </c>
     </row>
     <row r="35">
@@ -1366,10 +1366,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.408033161711585</v>
+        <v>0.407980180797016</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0310715690382773</v>
+        <v>0.0310616201315237</v>
       </c>
     </row>
     <row r="36">
@@ -1380,10 +1380,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.357219140056316</v>
+        <v>0.357279560126297</v>
       </c>
       <c r="D36" t="n">
-        <v>0.252127639540736</v>
+        <v>0.252170677786732</v>
       </c>
     </row>
     <row r="37">
@@ -1394,10 +1394,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.334749590933823</v>
+        <v>0.334564154854539</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0452619121282305</v>
+        <v>0.0452322903980648</v>
       </c>
     </row>
     <row r="38">
@@ -1408,10 +1408,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.29649073760912</v>
+        <v>0.296325989892793</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0213618126334314</v>
+        <v>0.0213481498557503</v>
       </c>
     </row>
     <row r="39">
@@ -1422,10 +1422,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.243486653425986</v>
+        <v>0.243569760489407</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0692200457348345</v>
+        <v>0.0692346973830037</v>
       </c>
     </row>
     <row r="40">
@@ -1436,10 +1436,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.237354733382793</v>
+        <v>0.237535707569507</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0633840758585622</v>
+        <v>0.0634142931010395</v>
       </c>
     </row>
     <row r="41">
@@ -1450,10 +1450,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.221633650996685</v>
+        <v>0.221687312715364</v>
       </c>
       <c r="D41" t="n">
-        <v>0.039385882664995</v>
+        <v>0.0393978215493857</v>
       </c>
     </row>
     <row r="42">
@@ -1464,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.218362436984872</v>
+        <v>0.218341710376351</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0268074220441333</v>
+        <v>0.0267940006818192</v>
       </c>
     </row>
     <row r="43">
@@ -1478,10 +1478,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.215403885861381</v>
+        <v>0.21556989052782</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0140755165261721</v>
+        <v>0.0140897760127736</v>
       </c>
     </row>
     <row r="44">
@@ -1492,10 +1492,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.203732560340298</v>
+        <v>0.203716946995462</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0996350379432133</v>
+        <v>0.0996276341787786</v>
       </c>
     </row>
     <row r="45">
@@ -1506,10 +1506,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.201168283249627</v>
+        <v>0.20140309448195</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0681503535556583</v>
+        <v>0.0682328603749471</v>
       </c>
     </row>
     <row r="46">
@@ -1520,10 +1520,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.196346163221418</v>
+        <v>0.196525967818807</v>
       </c>
       <c r="D46" t="n">
-        <v>0.042057155666971</v>
+        <v>0.0421406587788283</v>
       </c>
     </row>
     <row r="47">
@@ -1534,10 +1534,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1762094470845</v>
+        <v>0.176457205964325</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0987560773911232</v>
+        <v>0.0988979998929312</v>
       </c>
     </row>
     <row r="48">
@@ -1548,10 +1548,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.173365122136209</v>
+        <v>0.173777381480502</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0767428536724862</v>
+        <v>0.0769494542869134</v>
       </c>
     </row>
     <row r="49">
@@ -1562,10 +1562,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.171529312791459</v>
+        <v>0.171436278342176</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0439369793757112</v>
+        <v>0.0439091287331763</v>
       </c>
     </row>
     <row r="50">
@@ -1576,10 +1576,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.158452941556705</v>
+        <v>0.158406264655942</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0320443011426758</v>
+        <v>0.0320277246410673</v>
       </c>
     </row>
     <row r="51">
@@ -1590,10 +1590,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.150658243489545</v>
+        <v>0.150775942672018</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0156014830891205</v>
+        <v>0.0156130501490162</v>
       </c>
     </row>
     <row r="52">
@@ -1604,10 +1604,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.149869106882</v>
+        <v>0.150007435842705</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0167311560944157</v>
+        <v>0.0167569515158272</v>
       </c>
     </row>
     <row r="53">
@@ -1618,10 +1618,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.146747431559833</v>
+        <v>0.146718197206097</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0177707703748215</v>
+        <v>0.0177588930493906</v>
       </c>
     </row>
     <row r="54">
@@ -1632,10 +1632,10 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.146525796486527</v>
+        <v>0.146569446043663</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0117236325032513</v>
+        <v>0.0117307811754867</v>
       </c>
     </row>
     <row r="55">
@@ -1646,10 +1646,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.14390320470186</v>
+        <v>0.143856636540954</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0274590723172709</v>
+        <v>0.027443408100281</v>
       </c>
     </row>
     <row r="56">
@@ -1660,7 +1660,7 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.135992760059572</v>
+        <v>0.135993949067377</v>
       </c>
       <c r="D56"/>
     </row>
@@ -1672,10 +1672,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.120446033213541</v>
+        <v>0.120509516695025</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0112579446722338</v>
+        <v>0.0112652179141759</v>
       </c>
     </row>
     <row r="58">
@@ -1686,10 +1686,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.11958131801605</v>
+        <v>0.119661904634684</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00866643145246178</v>
+        <v>0.00867449478346747</v>
       </c>
     </row>
     <row r="59">
@@ -1700,10 +1700,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0969080353032679</v>
+        <v>0.0969286590258172</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0167313022770863</v>
+        <v>0.0167349750143522</v>
       </c>
     </row>
     <row r="60">
@@ -1714,10 +1714,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0954438901730593</v>
+        <v>0.0954200722779696</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0486010557125035</v>
+        <v>0.0485913367055212</v>
       </c>
     </row>
     <row r="61">
@@ -1728,10 +1728,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.092568372503675</v>
+        <v>0.092680306221937</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0302793212763506</v>
+        <v>0.0303196519633</v>
       </c>
     </row>
     <row r="62">
@@ -1742,10 +1742,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0921394725886354</v>
+        <v>0.0921400478814066</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0361739085241452</v>
+        <v>0.0361939575663574</v>
       </c>
     </row>
     <row r="63">
@@ -1756,7 +1756,7 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0785299804760684</v>
+        <v>0.0786780431751746</v>
       </c>
       <c r="D63"/>
     </row>
@@ -1768,7 +1768,7 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0720551857266377</v>
+        <v>0.0721662711184564</v>
       </c>
       <c r="D64"/>
     </row>
@@ -1780,10 +1780,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0715802324073418</v>
+        <v>0.0715711194329751</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0405298065431216</v>
+        <v>0.0405003938336102</v>
       </c>
     </row>
     <row r="66">
@@ -1794,10 +1794,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0695510870460006</v>
+        <v>0.0695941748240998</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00535412952095389</v>
+        <v>0.0053566548236333</v>
       </c>
     </row>
     <row r="67">
@@ -1808,10 +1808,10 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0681086689212079</v>
+        <v>0.0680993114124898</v>
       </c>
       <c r="D67" t="n">
-        <v>0.00915704037719756</v>
+        <v>0.00915575781347932</v>
       </c>
     </row>
     <row r="68">
@@ -1822,10 +1822,10 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0649945465535196</v>
+        <v>0.065033567108896</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00434718561093383</v>
+        <v>0.00435059276688745</v>
       </c>
     </row>
     <row r="69">
@@ -1836,10 +1836,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0624948128920292</v>
+        <v>0.0624930834998013</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00394678909664223</v>
+        <v>0.00394494268974948</v>
       </c>
     </row>
     <row r="70">
@@ -1850,10 +1850,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0616318633202602</v>
+        <v>0.0616127314801509</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0415193356762202</v>
+        <v>0.0415053329326085</v>
       </c>
     </row>
     <row r="71">
@@ -1864,10 +1864,10 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0607931420570137</v>
+        <v>0.0608148665136722</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0083334688702682</v>
+        <v>0.00833335922378025</v>
       </c>
     </row>
     <row r="72">
@@ -1878,10 +1878,10 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0602363323674261</v>
+        <v>0.0602336342120892</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00568001317934013</v>
+        <v>0.00567967026863827</v>
       </c>
     </row>
     <row r="73">
@@ -1892,10 +1892,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0596098785521259</v>
+        <v>0.059582510919524</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0124203080559801</v>
+        <v>0.0124120724949685</v>
       </c>
     </row>
     <row r="74">
@@ -1906,10 +1906,10 @@
         <v>77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0575434098248218</v>
+        <v>0.0575443014167302</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0168948027072683</v>
+        <v>0.016887169744277</v>
       </c>
     </row>
     <row r="75">
@@ -1920,10 +1920,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0544757822678205</v>
+        <v>0.0545037492375157</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00935947957057686</v>
+        <v>0.00937075209058937</v>
       </c>
     </row>
     <row r="76">
@@ -1934,10 +1934,10 @@
         <v>79</v>
       </c>
       <c r="C76" t="n">
-        <v>0.05405208113963</v>
+        <v>0.0540362735909604</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0126871422032338</v>
+        <v>0.0126792617628228</v>
       </c>
     </row>
     <row r="77">
@@ -1948,10 +1948,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0485683909623112</v>
+        <v>0.0486238387907147</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00490355501550665</v>
+        <v>0.00491257813716482</v>
       </c>
     </row>
     <row r="78">
@@ -1962,10 +1962,10 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0443305459127035</v>
+        <v>0.0443330416683277</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0154167540084506</v>
+        <v>0.0154125372708621</v>
       </c>
     </row>
     <row r="79">
@@ -1976,10 +1976,10 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0440020414380397</v>
+        <v>0.044077101447494</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0134851607703843</v>
+        <v>0.0135124285904939</v>
       </c>
     </row>
     <row r="80">
@@ -1990,10 +1990,10 @@
         <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0415121658534988</v>
+        <v>0.0415713182743147</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00669141911191948</v>
+        <v>0.00670402056267716</v>
       </c>
     </row>
     <row r="81">
@@ -2004,10 +2004,10 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0412155407321541</v>
+        <v>0.0412348514769146</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0123665869939431</v>
+        <v>0.0123801539706838</v>
       </c>
     </row>
     <row r="82">
@@ -2018,10 +2018,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0406932588344691</v>
+        <v>0.040699935435134</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00239731711558397</v>
+        <v>0.00239815938931361</v>
       </c>
     </row>
     <row r="83">
@@ -2032,10 +2032,10 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0374889914646262</v>
+        <v>0.0375223949531177</v>
       </c>
       <c r="D83" t="n">
-        <v>0.00476323010424525</v>
+        <v>0.00476729851308149</v>
       </c>
     </row>
     <row r="84">
@@ -2046,10 +2046,10 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0350908793724853</v>
+        <v>0.0351076759182588</v>
       </c>
       <c r="D84" t="n">
-        <v>0.000794947062707524</v>
+        <v>0.000795127397304217</v>
       </c>
     </row>
     <row r="85">
@@ -2060,10 +2060,10 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0341509779463198</v>
+        <v>0.0341499830965258</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00259081987262173</v>
+        <v>0.00258957490027071</v>
       </c>
     </row>
     <row r="86">
@@ -2074,10 +2074,10 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0307507261213028</v>
+        <v>0.030754388604075</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00197715275920604</v>
+        <v>0.00197753320651106</v>
       </c>
     </row>
     <row r="87">
@@ -2088,10 +2088,10 @@
         <v>90</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0300777284501567</v>
+        <v>0.0301208605890432</v>
       </c>
       <c r="D87" t="n">
-        <v>0.020139118314993</v>
+        <v>0.0201703826344658</v>
       </c>
     </row>
     <row r="88">
@@ -2102,10 +2102,10 @@
         <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0291765236544047</v>
+        <v>0.029189291118077</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0139655288351434</v>
+        <v>0.013951834600167</v>
       </c>
     </row>
     <row r="89">
@@ -2116,10 +2116,10 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>0.025821344330465</v>
+        <v>0.0258174183925515</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00601232086736538</v>
+        <v>0.00600843504328905</v>
       </c>
     </row>
     <row r="90">
@@ -2130,10 +2130,10 @@
         <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0233101341017797</v>
+        <v>0.0233352589624671</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0102560693190483</v>
+        <v>0.0102714703304323</v>
       </c>
     </row>
     <row r="91">
@@ -2144,10 +2144,10 @@
         <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0226663183002104</v>
+        <v>0.0226923206597295</v>
       </c>
       <c r="D91" t="n">
-        <v>0.000510630741798756</v>
+        <v>0.000488589558150084</v>
       </c>
     </row>
     <row r="92">
@@ -2158,10 +2158,10 @@
         <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0225034883724881</v>
+        <v>0.0225105844784098</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00511665459270525</v>
+        <v>0.00511740960582774</v>
       </c>
     </row>
     <row r="93">
@@ -2172,10 +2172,10 @@
         <v>96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0212579375157307</v>
+        <v>0.0212618098926915</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00483788808695239</v>
+        <v>0.00483651825215603</v>
       </c>
     </row>
     <row r="94">
@@ -2186,10 +2186,10 @@
         <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0204730678370141</v>
+        <v>0.0204884508837802</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00375852070875376</v>
+        <v>0.0037621171971516</v>
       </c>
     </row>
     <row r="95">
@@ -2200,10 +2200,10 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0191791584535295</v>
+        <v>0.0191751766177445</v>
       </c>
       <c r="D95" t="n">
-        <v>0.00459493335373274</v>
+        <v>0.00459429935420734</v>
       </c>
     </row>
     <row r="96">
@@ -2214,7 +2214,7 @@
         <v>99</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0180970260664018</v>
+        <v>0.0181067658797221</v>
       </c>
       <c r="D96"/>
     </row>
@@ -2226,10 +2226,10 @@
         <v>100</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0156093575140137</v>
+        <v>0.0156151961619319</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00572188063415783</v>
+        <v>0.00572530867624686</v>
       </c>
     </row>
     <row r="98">
@@ -2240,7 +2240,7 @@
         <v>101</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0149403815459018</v>
+        <v>0.0149545155459154</v>
       </c>
       <c r="D98"/>
     </row>
@@ -2252,7 +2252,7 @@
         <v>102</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0146018718588117</v>
+        <v>0.014619028986818</v>
       </c>
       <c r="D99"/>
     </row>
@@ -2264,10 +2264,10 @@
         <v>103</v>
       </c>
       <c r="C100" t="n">
-        <v>0.01374887845431</v>
+        <v>0.0137473030642314</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00245762675404466</v>
+        <v>0.00245600218885046</v>
       </c>
     </row>
     <row r="101">
@@ -2278,10 +2278,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0137053263531602</v>
+        <v>0.0137139749619397</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00148130815089699</v>
+        <v>0.00148222010394328</v>
       </c>
     </row>
     <row r="102">
@@ -2292,10 +2292,10 @@
         <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0135151292267424</v>
+        <v>0.0135246419337742</v>
       </c>
       <c r="D102" t="n">
-        <v>0.00798403278634667</v>
+        <v>0.00798759711897541</v>
       </c>
     </row>
     <row r="103">
@@ -2306,10 +2306,10 @@
         <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0130467479587462</v>
+        <v>0.0130673117536518</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00321573199456767</v>
+        <v>0.00321928941579555</v>
       </c>
     </row>
     <row r="104">
@@ -2320,10 +2320,10 @@
         <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0125099977391701</v>
+        <v>0.012518182256482</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0022069061650978</v>
+        <v>0.00220871676391359</v>
       </c>
     </row>
     <row r="105">
@@ -2334,7 +2334,7 @@
         <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0121509871756379</v>
+        <v>0.0121648553602756</v>
       </c>
       <c r="D105"/>
     </row>
@@ -2346,10 +2346,10 @@
         <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0120555943414753</v>
+        <v>0.01205550977761</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0014792038305162</v>
+        <v>0.00147852929335601</v>
       </c>
     </row>
     <row r="107">
@@ -2360,7 +2360,7 @@
         <v>110</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0119720213906203</v>
+        <v>0.0119710622478328</v>
       </c>
       <c r="D107"/>
     </row>
@@ -2372,7 +2372,7 @@
         <v>111</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0117311115698457</v>
+        <v>0.0117546746425129</v>
       </c>
       <c r="D108"/>
     </row>
@@ -2384,10 +2384,10 @@
         <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>0.011254883076417</v>
+        <v>0.0112678883013945</v>
       </c>
       <c r="D109" t="n">
-        <v>0.000325299942819365</v>
+        <v>0.000328441143608196</v>
       </c>
     </row>
     <row r="110">
@@ -2398,7 +2398,7 @@
         <v>113</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0108779710298671</v>
+        <v>0.0108960839131823</v>
       </c>
       <c r="D110"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0105551557936419</v>
+        <v>0.0105630969617568</v>
       </c>
       <c r="D111" t="n">
-        <v>0.00287320239231331</v>
+        <v>0.00287417205853787</v>
       </c>
     </row>
     <row r="112">
@@ -2424,10 +2424,10 @@
         <v>115</v>
       </c>
       <c r="C112" t="n">
-        <v>0.00975596492851107</v>
+        <v>0.0097600367322739</v>
       </c>
       <c r="D112" t="n">
-        <v>0.00150195841456685</v>
+        <v>0.00150399675458552</v>
       </c>
     </row>
     <row r="113">
@@ -2438,10 +2438,10 @@
         <v>116</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00925143737836682</v>
+        <v>0.00925452783957407</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00199571957585564</v>
+        <v>0.0019968602819696</v>
       </c>
     </row>
     <row r="114">
@@ -2452,10 +2452,10 @@
         <v>117</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00835660845327867</v>
+        <v>0.00835873706665621</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0017075138159926</v>
+        <v>0.0017071599188365</v>
       </c>
     </row>
     <row r="115">
@@ -2466,7 +2466,7 @@
         <v>118</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00820486273147968</v>
+        <v>0.00820111474758285</v>
       </c>
       <c r="D115"/>
     </row>
@@ -2478,10 +2478,10 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00763745928755834</v>
+        <v>0.00763257653201973</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00497289282523427</v>
+        <v>0.00496931415622544</v>
       </c>
     </row>
     <row r="117">
@@ -2492,10 +2492,10 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00708491652679961</v>
+        <v>0.00709138696510181</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00112138311845034</v>
+        <v>0.00112069233521771</v>
       </c>
     </row>
     <row r="118">
@@ -2506,7 +2506,7 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00556848925714762</v>
+        <v>0.00556677332100509</v>
       </c>
       <c r="D118"/>
     </row>
@@ -2518,7 +2518,7 @@
         <v>122</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00526151560726399</v>
+        <v>0.00526216426844261</v>
       </c>
       <c r="D119"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00526048565892599</v>
+        <v>0.00525922355353452</v>
       </c>
       <c r="D120" t="n">
-        <v>0.000968486027812199</v>
+        <v>0.00096797051640928</v>
       </c>
     </row>
     <row r="121">
@@ -2544,7 +2544,7 @@
         <v>124</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00462755788264413</v>
+        <v>0.00462574455041786</v>
       </c>
       <c r="D121"/>
     </row>
@@ -2556,10 +2556,10 @@
         <v>125</v>
       </c>
       <c r="C122" t="n">
-        <v>0.00437355300442919</v>
+        <v>0.0043747545330128</v>
       </c>
       <c r="D122" t="n">
-        <v>0.00262813222459885</v>
+        <v>0.00262929663840066</v>
       </c>
     </row>
     <row r="123">
@@ -2570,7 +2570,7 @@
         <v>126</v>
       </c>
       <c r="C123" t="n">
-        <v>0.00413274127397247</v>
+        <v>0.00413503725608872</v>
       </c>
       <c r="D123"/>
     </row>
@@ -2582,10 +2582,10 @@
         <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>0.00349515420759013</v>
+        <v>0.00349391239421104</v>
       </c>
       <c r="D124" t="n">
-        <v>0.000966050661745871</v>
+        <v>0.000966192955856591</v>
       </c>
     </row>
     <row r="125">
@@ -2596,10 +2596,10 @@
         <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>0.00332339806093851</v>
+        <v>0.0033243311678448</v>
       </c>
       <c r="D125" t="n">
-        <v>0.000373702678555476</v>
+        <v>0.0003740829949029</v>
       </c>
     </row>
     <row r="126">
@@ -2610,10 +2610,10 @@
         <v>129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.00269738565206895</v>
+        <v>0.00269555730858107</v>
       </c>
       <c r="D126" t="n">
-        <v>0.000978535520958555</v>
+        <v>0.000977872249451185</v>
       </c>
     </row>
     <row r="127">
@@ -2624,7 +2624,7 @@
         <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>0.00260424889521818</v>
+        <v>0.0026112568145493</v>
       </c>
       <c r="D127"/>
     </row>
@@ -2636,10 +2636,10 @@
         <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>0.00256373759392342</v>
+        <v>0.00256312711388697</v>
       </c>
       <c r="D128" t="n">
-        <v>0.000683788803045783</v>
+        <v>0.000684122420051261</v>
       </c>
     </row>
     <row r="129">
@@ -2650,7 +2650,7 @@
         <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>0.00246628486308483</v>
+        <v>0.00246686771256232</v>
       </c>
       <c r="D129"/>
     </row>
@@ -2662,7 +2662,7 @@
         <v>133</v>
       </c>
       <c r="C130" t="n">
-        <v>0.00205244181184373</v>
+        <v>0.00205207987477692</v>
       </c>
       <c r="D130"/>
     </row>
@@ -2674,7 +2674,7 @@
         <v>134</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0016419338314114</v>
+        <v>0.00164082089488121</v>
       </c>
       <c r="D131"/>
     </row>
@@ -2686,10 +2686,10 @@
         <v>135</v>
       </c>
       <c r="C132" t="n">
-        <v>0.00152579489501191</v>
+        <v>0.00152711325176859</v>
       </c>
       <c r="D132" t="n">
-        <v>0.000382244772894996</v>
+        <v>0.000383649199086497</v>
       </c>
     </row>
     <row r="133">
@@ -2700,7 +2700,7 @@
         <v>136</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0015118660698694</v>
+        <v>0.00151226264148276</v>
       </c>
       <c r="D133"/>
     </row>
@@ -2712,7 +2712,7 @@
         <v>137</v>
       </c>
       <c r="C134" t="n">
-        <v>0.00142824407385541</v>
+        <v>0.00143310839854014</v>
       </c>
       <c r="D134"/>
     </row>
@@ -2724,7 +2724,7 @@
         <v>138</v>
       </c>
       <c r="C135" t="n">
-        <v>0.00140911646186394</v>
+        <v>0.00141031785800248</v>
       </c>
       <c r="D135"/>
     </row>
@@ -2736,10 +2736,10 @@
         <v>139</v>
       </c>
       <c r="C136" t="n">
-        <v>0.00138670282422265</v>
+        <v>0.0013893407583248</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0000293394191498065</v>
+        <v>0.0000309483951927951</v>
       </c>
     </row>
     <row r="137">
@@ -2750,7 +2750,7 @@
         <v>140</v>
       </c>
       <c r="C137" t="n">
-        <v>0.00123956734736519</v>
+        <v>0.00124137378653299</v>
       </c>
       <c r="D137"/>
     </row>
@@ -2762,10 +2762,10 @@
         <v>141</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00123956734736519</v>
+        <v>0.00124137378653299</v>
       </c>
       <c r="D138" t="n">
-        <v>0.000270574643270437</v>
+        <v>0.000269767422374824</v>
       </c>
     </row>
     <row r="139">
@@ -2776,7 +2776,7 @@
         <v>142</v>
       </c>
       <c r="C139" t="n">
-        <v>0.00122583470285849</v>
+        <v>0.00122549392602933</v>
       </c>
       <c r="D139"/>
     </row>
@@ -2788,7 +2788,7 @@
         <v>143</v>
       </c>
       <c r="C140" t="n">
-        <v>0.00112102519817703</v>
+        <v>0.00112129459445285</v>
       </c>
       <c r="D140"/>
     </row>
@@ -2800,7 +2800,7 @@
         <v>144</v>
       </c>
       <c r="C141" t="n">
-        <v>0.00108149480006132</v>
+        <v>0.00108193802659964</v>
       </c>
       <c r="D141"/>
     </row>
@@ -2812,7 +2812,7 @@
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>0.00100160023612772</v>
+        <v>0.00100121540237271</v>
       </c>
       <c r="D142"/>
     </row>
@@ -2824,7 +2824,7 @@
         <v>146</v>
       </c>
       <c r="C143" t="n">
-        <v>0.000969181386060122</v>
+        <v>0.00097092603881943</v>
       </c>
       <c r="D143"/>
     </row>
@@ -2836,7 +2836,7 @@
         <v>147</v>
       </c>
       <c r="C144" t="n">
-        <v>0.000798357097428605</v>
+        <v>0.000797815954563487</v>
       </c>
       <c r="D144"/>
     </row>
@@ -2848,10 +2848,10 @@
         <v>148</v>
       </c>
       <c r="C145" t="n">
-        <v>0.000795463433050408</v>
+        <v>0.000797521883072678</v>
       </c>
       <c r="D145" t="n">
-        <v>0.000245431524022671</v>
+        <v>0.000246755401761144</v>
       </c>
     </row>
     <row r="146">
@@ -2862,7 +2862,7 @@
         <v>149</v>
       </c>
       <c r="C146" t="n">
-        <v>0.000755933034934702</v>
+        <v>0.000756106814783813</v>
       </c>
       <c r="D146"/>
     </row>
@@ -2874,7 +2874,7 @@
         <v>150</v>
       </c>
       <c r="C147" t="n">
-        <v>0.000755933034934702</v>
+        <v>0.000756106814783813</v>
       </c>
       <c r="D147"/>
     </row>
@@ -2886,7 +2886,7 @@
         <v>151</v>
       </c>
       <c r="C148" t="n">
-        <v>0.000453569629992612</v>
+        <v>0.000453654286487261</v>
       </c>
       <c r="D148"/>
     </row>
@@ -2898,7 +2898,7 @@
         <v>152</v>
       </c>
       <c r="C149" t="n">
-        <v>0.000428458508608938</v>
+        <v>0.000429932519562041</v>
       </c>
       <c r="D149"/>
     </row>
@@ -2910,7 +2910,7 @@
         <v>153</v>
       </c>
       <c r="C150" t="n">
-        <v>0.000285639005739292</v>
+        <v>0.000286621679708027</v>
       </c>
       <c r="D150"/>
     </row>
@@ -2922,7 +2922,7 @@
         <v>154</v>
       </c>
       <c r="C151" t="n">
-        <v>0.000285639005739292</v>
+        <v>0.000286621679708027</v>
       </c>
       <c r="D151"/>
     </row>
@@ -2934,7 +2934,7 @@
         <v>155</v>
       </c>
       <c r="C152" t="n">
-        <v>0.000224185421571824</v>
+        <v>0.000224278523656623</v>
       </c>
       <c r="D152"/>
     </row>
@@ -2946,7 +2946,7 @@
         <v>156</v>
       </c>
       <c r="C153" t="n">
-        <v>0.000224185421571824</v>
+        <v>0.000224278523656623</v>
       </c>
       <c r="D153"/>
     </row>
@@ -2983,10 +2983,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>18.2027915718889</v>
+        <v>18.6701967120886</v>
       </c>
       <c r="D2" t="n">
-        <v>5.77663965540794</v>
+        <v>5.92472741205995</v>
       </c>
     </row>
     <row r="3">
@@ -2997,10 +2997,10 @@
         <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>15.6973862252791</v>
+        <v>16.070041990206</v>
       </c>
       <c r="D3" t="n">
-        <v>5.02283991220684</v>
+        <v>5.14196444827811</v>
       </c>
     </row>
     <row r="4">
@@ -3011,10 +3011,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>11.9843198691813</v>
+        <v>11.5675003162001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.943501140912699</v>
+        <v>0.904166644289238</v>
       </c>
     </row>
     <row r="5">
@@ -3025,10 +3025,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>10.6823484590553</v>
+        <v>10.8796597564902</v>
       </c>
       <c r="D5" t="n">
-        <v>1.00582915340246</v>
+        <v>1.02396205701846</v>
       </c>
     </row>
     <row r="6">
@@ -3039,10 +3039,10 @@
         <v>88</v>
       </c>
       <c r="C6" t="n">
-        <v>9.79478204815961</v>
+        <v>9.97805148997987</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0992693095626868</v>
+        <v>0.101104074678197</v>
       </c>
     </row>
     <row r="7">
@@ -3053,10 +3053,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>8.79152197915228</v>
+        <v>8.93364668343104</v>
       </c>
       <c r="D7" t="n">
-        <v>0.276548902635869</v>
+        <v>0.282798044666984</v>
       </c>
     </row>
     <row r="8">
@@ -3067,10 +3067,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>5.11612432800576</v>
+        <v>5.17242596287836</v>
       </c>
       <c r="D8" t="n">
-        <v>0.331146793229537</v>
+        <v>0.334982500993478</v>
       </c>
     </row>
     <row r="9">
@@ -3078,13 +3078,13 @@
         <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>2.56147148901099</v>
+        <v>2.38217123422964</v>
       </c>
       <c r="D9" t="n">
-        <v>0.280781040911208</v>
+        <v>0.327412981786058</v>
       </c>
     </row>
     <row r="10">
@@ -3092,13 +3092,13 @@
         <v>157</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2.36233037787507</v>
+        <v>1.90579847666764</v>
       </c>
       <c r="D10" t="n">
-        <v>0.323410666991293</v>
+        <v>0.0945598637090278</v>
       </c>
     </row>
     <row r="11">
@@ -3106,13 +3106,13 @@
         <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>1.89341358011806</v>
+        <v>1.43546687764993</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0931556428473659</v>
+        <v>0.170722403007775</v>
       </c>
     </row>
     <row r="12">
@@ -3123,10 +3123,10 @@
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>0.902877137599435</v>
+        <v>0.919470021285635</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0900063018970212</v>
+        <v>0.0916927716374278</v>
       </c>
     </row>
     <row r="13">
@@ -3134,13 +3134,13 @@
         <v>157</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.878232655697776</v>
+        <v>0.880688739025582</v>
       </c>
       <c r="D13" t="n">
-        <v>0.069283452112643</v>
+        <v>0.0371052650658224</v>
       </c>
     </row>
     <row r="14">
@@ -3148,13 +3148,13 @@
         <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>0.865317829284429</v>
+        <v>0.850521879300816</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0364235675520544</v>
+        <v>0.0659782711014294</v>
       </c>
     </row>
     <row r="15">
@@ -3165,10 +3165,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>0.70664940377435</v>
+        <v>0.717771377787698</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0220874560505524</v>
+        <v>0.0224540796301357</v>
       </c>
     </row>
     <row r="16">
@@ -3179,10 +3179,10 @@
         <v>40</v>
       </c>
       <c r="C16" t="n">
-        <v>0.652979365154297</v>
+        <v>0.665537047028901</v>
       </c>
       <c r="D16" t="n">
-        <v>0.140077795474625</v>
+        <v>0.142766217725096</v>
       </c>
     </row>
     <row r="17">
@@ -3190,13 +3190,13 @@
         <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>0.618075570650204</v>
+        <v>0.629995072929862</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0255714907708922</v>
+        <v>0.0515250664081847</v>
       </c>
     </row>
     <row r="18">
@@ -3204,13 +3204,13 @@
         <v>157</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C18" t="n">
-        <v>0.617955144814306</v>
+        <v>0.624525525329569</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0505896274415744</v>
+        <v>0.0730272179669928</v>
       </c>
     </row>
     <row r="19">
@@ -3218,13 +3218,13 @@
         <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>0.613627669465594</v>
+        <v>0.608751531792866</v>
       </c>
       <c r="D19" t="n">
-        <v>0.071740649854671</v>
+        <v>0.0245354855909901</v>
       </c>
     </row>
     <row r="20">
@@ -3235,10 +3235,10 @@
         <v>158</v>
       </c>
       <c r="C20" t="n">
-        <v>0.59022171376807</v>
+        <v>0.601254113499933</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0202054733286437</v>
+        <v>0.0205709171270145</v>
       </c>
     </row>
     <row r="21">
@@ -3249,10 +3249,10 @@
         <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>0.526855706384887</v>
+        <v>0.536293704410427</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0180429191389399</v>
+        <v>0.0183211795699311</v>
       </c>
     </row>
     <row r="22">
@@ -3260,13 +3260,13 @@
         <v>157</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>0.40282714785413</v>
+        <v>0.407642474686338</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0946477811499876</v>
+        <v>0.0126559694143574</v>
       </c>
     </row>
     <row r="23">
@@ -3274,13 +3274,13 @@
         <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>0.399959555965873</v>
+        <v>0.393394861710404</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0124168509240596</v>
+        <v>0.0911584562012848</v>
       </c>
     </row>
     <row r="24">
@@ -3291,10 +3291,10 @@
         <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>0.371767049749335</v>
+        <v>0.375392989565071</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0257864675354967</v>
+        <v>0.026162965153018</v>
       </c>
     </row>
     <row r="25">
@@ -3305,10 +3305,10 @@
         <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>0.353583969473382</v>
+        <v>0.35956974992936</v>
       </c>
       <c r="D25" t="n">
-        <v>0.127778130706983</v>
+        <v>0.130054544070556</v>
       </c>
     </row>
     <row r="26">
@@ -3319,7 +3319,7 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>0.340713463349083</v>
+        <v>0.346740499157414</v>
       </c>
       <c r="D26"/>
     </row>
@@ -3331,10 +3331,10 @@
         <v>18</v>
       </c>
       <c r="C27" t="n">
-        <v>0.290559012615653</v>
+        <v>0.296051062841857</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0214373312672283</v>
+        <v>0.0218399348668751</v>
       </c>
     </row>
     <row r="28">
@@ -3345,10 +3345,10 @@
         <v>14</v>
       </c>
       <c r="C28" t="n">
-        <v>0.27964075621159</v>
+        <v>0.276278236363976</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0488775596481117</v>
+        <v>0.0470761403137777</v>
       </c>
     </row>
     <row r="29">
@@ -3356,13 +3356,13 @@
         <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>0.232046422817513</v>
+        <v>0.234118564024938</v>
       </c>
       <c r="D29" t="n">
-        <v>0.130370466605562</v>
+        <v>0.00641127799690849</v>
       </c>
     </row>
     <row r="30">
@@ -3370,13 +3370,13 @@
         <v>157</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C30" t="n">
-        <v>0.230797233697187</v>
+        <v>0.220887557861587</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00632689816038339</v>
+        <v>0.123856900643707</v>
       </c>
     </row>
     <row r="31">
@@ -3387,10 +3387,10 @@
         <v>116</v>
       </c>
       <c r="C31" t="n">
-        <v>0.214587199897855</v>
+        <v>0.210242034023298</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0823358369505311</v>
+        <v>0.0804794384152782</v>
       </c>
     </row>
     <row r="32">
@@ -3401,10 +3401,10 @@
         <v>61</v>
       </c>
       <c r="C32" t="n">
-        <v>0.187375722668919</v>
+        <v>0.185013203657803</v>
       </c>
       <c r="D32" t="n">
-        <v>0.025162953520189</v>
+        <v>0.0242359873692432</v>
       </c>
     </row>
     <row r="33">
@@ -3415,10 +3415,10 @@
         <v>48</v>
       </c>
       <c r="C33" t="n">
-        <v>0.150464858031966</v>
+        <v>0.154444257196979</v>
       </c>
       <c r="D33" t="n">
-        <v>0.104549997918908</v>
+        <v>0.107314532304328</v>
       </c>
     </row>
     <row r="34">
@@ -3429,10 +3429,10 @@
         <v>136</v>
       </c>
       <c r="C34" t="n">
-        <v>0.147049346904543</v>
+        <v>0.149653427699671</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0834521571631023</v>
+        <v>0.0849275595119704</v>
       </c>
     </row>
     <row r="35">
@@ -3443,10 +3443,10 @@
         <v>35</v>
       </c>
       <c r="C35" t="n">
-        <v>0.143469822218936</v>
+        <v>0.146248778556958</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00500190534289163</v>
+        <v>0.00509910821812543</v>
       </c>
     </row>
     <row r="36">
@@ -3457,10 +3457,10 @@
         <v>22</v>
       </c>
       <c r="C36" t="n">
-        <v>0.125453400881138</v>
+        <v>0.127947412263661</v>
       </c>
       <c r="D36" t="n">
-        <v>0.025434173013074</v>
+        <v>0.0259050361153104</v>
       </c>
     </row>
     <row r="37">
@@ -3471,10 +3471,10 @@
         <v>24</v>
       </c>
       <c r="C37" t="n">
-        <v>0.122462493588092</v>
+        <v>0.124905544097579</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0836731562778796</v>
+        <v>0.0853439473031053</v>
       </c>
     </row>
     <row r="38">
@@ -3485,10 +3485,10 @@
         <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>0.117831206524281</v>
+        <v>0.120639398857831</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0172624127188552</v>
+        <v>0.0176981062984511</v>
       </c>
     </row>
     <row r="39">
@@ -3499,10 +3499,10 @@
         <v>87</v>
       </c>
       <c r="C39" t="n">
-        <v>0.109632604220882</v>
+        <v>0.111072277609854</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00375386967910732</v>
+        <v>0.00377827799911721</v>
       </c>
     </row>
     <row r="40">
@@ -3513,10 +3513,10 @@
         <v>25</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0967866390830805</v>
+        <v>0.0986052279613971</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0286470406976744</v>
+        <v>0.0291767539358545</v>
       </c>
     </row>
     <row r="41">
@@ -3527,10 +3527,10 @@
         <v>120</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0918020513496421</v>
+        <v>0.0941623517675124</v>
       </c>
       <c r="D41" t="n">
-        <v>0.060602054248835</v>
+        <v>0.062187326405534</v>
       </c>
     </row>
     <row r="42">
@@ -3538,13 +3538,13 @@
         <v>157</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0902018406562787</v>
+        <v>0.0912362057213875</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0231583387517596</v>
+        <v>0.0193971811413125</v>
       </c>
     </row>
     <row r="43">
@@ -3552,13 +3552,13 @@
         <v>157</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0892378234967961</v>
+        <v>0.0881901543290649</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0189536723321098</v>
+        <v>0.010461708709322</v>
       </c>
     </row>
     <row r="44">
@@ -3566,13 +3566,13 @@
         <v>157</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0864561861085105</v>
+        <v>0.0872037412979602</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0102586727118515</v>
+        <v>0.0220175666011216</v>
       </c>
     </row>
     <row r="45">
@@ -3583,10 +3583,10 @@
         <v>72</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0770749361655871</v>
+        <v>0.0762249675752125</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00912377071050955</v>
+        <v>0.00876980825981953</v>
       </c>
     </row>
     <row r="46">
@@ -3594,13 +3594,13 @@
         <v>157</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0762022049641709</v>
+        <v>0.0743941226966877</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0175851118125976</v>
+        <v>0.02825215523625</v>
       </c>
     </row>
     <row r="47">
@@ -3608,13 +3608,13 @@
         <v>157</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0729773646854068</v>
+        <v>0.0736319471593016</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0277141031745769</v>
+        <v>0.0166506737171187</v>
       </c>
     </row>
     <row r="48">
@@ -3625,10 +3625,10 @@
         <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0719791203789184</v>
+        <v>0.0730815008549944</v>
       </c>
       <c r="D48" t="n">
-        <v>0.011506782768742</v>
+        <v>0.0117432588892418</v>
       </c>
     </row>
     <row r="49">
@@ -3639,10 +3639,10 @@
         <v>26</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0698829212901223</v>
+        <v>0.0679469426985866</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0218629882059685</v>
+        <v>0.021058119293667</v>
       </c>
     </row>
     <row r="50">
@@ -3653,10 +3653,10 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0638503968048994</v>
+        <v>0.0650791547294196</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0089493144892054</v>
+        <v>0.00912214435057109</v>
       </c>
     </row>
     <row r="51">
@@ -3664,13 +3664,13 @@
         <v>157</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0595077003468171</v>
+        <v>0.059654007312589</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0131829848966438</v>
+        <v>0.0256086462176168</v>
       </c>
     </row>
     <row r="52">
@@ -3678,13 +3678,13 @@
         <v>157</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0584668043755701</v>
+        <v>0.0582030490783911</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0252007847191451</v>
+        <v>0.0125557585312763</v>
       </c>
     </row>
     <row r="53">
@@ -3695,10 +3695,10 @@
         <v>36</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0562038649523121</v>
+        <v>0.0572920997919402</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00864562633884191</v>
+        <v>0.00881441410973435</v>
       </c>
     </row>
     <row r="54">
@@ -3709,10 +3709,10 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0535564907720787</v>
+        <v>0.0545293894957624</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0215733440917537</v>
+        <v>0.021957881944754</v>
       </c>
     </row>
     <row r="55">
@@ -3723,10 +3723,10 @@
         <v>38</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0514403495881188</v>
+        <v>0.0526450738739072</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00551911166751127</v>
+        <v>0.00566135012596707</v>
       </c>
     </row>
     <row r="56">
@@ -3734,13 +3734,13 @@
         <v>157</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0490028150867934</v>
+        <v>0.0476558931838741</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0334037351412075</v>
+        <v>0.00593513006733561</v>
       </c>
     </row>
     <row r="57">
@@ -3748,13 +3748,13 @@
         <v>157</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0474518491590388</v>
+        <v>0.0464996246001762</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00577317823680763</v>
+        <v>0.0316116624841636</v>
       </c>
     </row>
     <row r="58">
@@ -3765,10 +3765,10 @@
         <v>82</v>
       </c>
       <c r="C58" t="n">
-        <v>0.04577187008502</v>
+        <v>0.0464306634943319</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0110486861880588</v>
+        <v>0.011248997805745</v>
       </c>
     </row>
     <row r="59">
@@ -3779,10 +3779,10 @@
         <v>60</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0355302204811593</v>
+        <v>0.0361628725601272</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0164048763394693</v>
+        <v>0.0166943860503811</v>
       </c>
     </row>
     <row r="60">
@@ -3793,10 +3793,10 @@
         <v>75</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0330345283186315</v>
+        <v>0.0327733410171936</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00444657428805936</v>
+        <v>0.00424541341835407</v>
       </c>
     </row>
     <row r="61">
@@ -3807,10 +3807,10 @@
         <v>77</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0305731853975697</v>
+        <v>0.0311983770467207</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0101962494999458</v>
+        <v>0.0104164105364722</v>
       </c>
     </row>
     <row r="62">
@@ -3821,10 +3821,10 @@
         <v>31</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0266525287902002</v>
+        <v>0.027170178685697</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00808206999742258</v>
+        <v>0.00823950807632378</v>
       </c>
     </row>
     <row r="63">
@@ -3835,10 +3835,10 @@
         <v>117</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0257027152862527</v>
+        <v>0.0249930786450947</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00575395422531317</v>
+        <v>0.00544470079196906</v>
       </c>
     </row>
     <row r="64">
@@ -3849,10 +3849,10 @@
         <v>159</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0243428271886906</v>
+        <v>0.0249564236428892</v>
       </c>
       <c r="D64" t="n">
-        <v>0.011380495472467</v>
+        <v>0.0117112002401203</v>
       </c>
     </row>
     <row r="65">
@@ -3863,10 +3863,10 @@
         <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0235232884737625</v>
+        <v>0.0239898084547837</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0036354901924624</v>
+        <v>0.00370400549885203</v>
       </c>
     </row>
     <row r="66">
@@ -3877,10 +3877,10 @@
         <v>160</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0213826876996117</v>
+        <v>0.0217962240177094</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0110862122554927</v>
+        <v>0.0113003035409631</v>
       </c>
     </row>
     <row r="67">
@@ -3888,26 +3888,26 @@
         <v>157</v>
       </c>
       <c r="B67" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0196860223827007</v>
-      </c>
-      <c r="D67"/>
+        <v>0.0196346971757843</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.00534039138515961</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
         <v>157</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0192689884048555</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0.00524453354264989</v>
-      </c>
+        <v>0.0186556151451209</v>
+      </c>
+      <c r="D68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0108635580858995</v>
+        <v>0.0111169858610075</v>
       </c>
       <c r="D69"/>
     </row>
@@ -3929,10 +3929,10 @@
         <v>89</v>
       </c>
       <c r="C70" t="n">
-        <v>0.00962775865804077</v>
+        <v>0.00981475995779291</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00119138837079778</v>
+        <v>0.00121443046524061</v>
       </c>
     </row>
     <row r="71">
@@ -3943,10 +3943,10 @@
         <v>69</v>
       </c>
       <c r="C71" t="n">
-        <v>0.00957419988817211</v>
+        <v>0.00975884554764884</v>
       </c>
       <c r="D71" t="n">
-        <v>0.000915413754476115</v>
+        <v>0.000933656303365945</v>
       </c>
     </row>
     <row r="72">
@@ -3957,10 +3957,10 @@
         <v>65</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00938316275613295</v>
+        <v>0.00955618687443777</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0010873169163838</v>
+        <v>0.00110842532950841</v>
       </c>
     </row>
     <row r="73">
@@ -3971,10 +3971,10 @@
         <v>55</v>
       </c>
       <c r="C73" t="n">
-        <v>0.00933456916097855</v>
+        <v>0.00951224228987269</v>
       </c>
       <c r="D73" t="n">
-        <v>0.00120576023809783</v>
+        <v>0.00123071375226856</v>
       </c>
     </row>
     <row r="74">
@@ -3985,10 +3985,10 @@
         <v>143</v>
       </c>
       <c r="C74" t="n">
-        <v>0.00865499139557807</v>
+        <v>0.00882304541224502</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00305998716449211</v>
+        <v>0.00311941762085765</v>
       </c>
     </row>
     <row r="75">
@@ -3999,10 +3999,10 @@
         <v>56</v>
       </c>
       <c r="C75" t="n">
-        <v>0.00837604625220432</v>
+        <v>0.00853929013528425</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00266388681285698</v>
+        <v>0.00271543450649814</v>
       </c>
     </row>
     <row r="76">
@@ -4013,10 +4013,10 @@
         <v>62</v>
       </c>
       <c r="C76" t="n">
-        <v>0.007949122623084</v>
+        <v>0.00812954105413217</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00147023618932144</v>
+        <v>0.00148678416460549</v>
       </c>
     </row>
     <row r="77">
@@ -4027,10 +4027,10 @@
         <v>149</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0063734529162182</v>
+        <v>0.00649385817605092</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00199349112978482</v>
+        <v>0.00202996915083978</v>
       </c>
     </row>
     <row r="78">
@@ -4041,7 +4041,7 @@
         <v>161</v>
       </c>
       <c r="C78" t="n">
-        <v>0.00619617176002677</v>
+        <v>0.00631646453260866</v>
       </c>
       <c r="D78"/>
     </row>
@@ -4053,10 +4053,10 @@
         <v>103</v>
       </c>
       <c r="C79" t="n">
-        <v>0.00613280473518975</v>
+        <v>0.00624833178839606</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00231143701672872</v>
+        <v>0.00235486090175442</v>
       </c>
     </row>
     <row r="80">
@@ -4067,10 +4067,10 @@
         <v>95</v>
       </c>
       <c r="C80" t="n">
-        <v>0.00604599557399684</v>
+        <v>0.00618964236678558</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00135426109012268</v>
+        <v>0.00139912815458571</v>
       </c>
     </row>
     <row r="81">
@@ -4081,7 +4081,7 @@
         <v>99</v>
       </c>
       <c r="C81" t="n">
-        <v>0.00509463554022024</v>
+        <v>0.00519689236919798</v>
       </c>
       <c r="D81"/>
     </row>
@@ -4093,10 +4093,10 @@
         <v>162</v>
       </c>
       <c r="C82" t="n">
-        <v>0.00462257765898416</v>
+        <v>0.00471230081461603</v>
       </c>
       <c r="D82" t="n">
-        <v>0.000904087770825857</v>
+        <v>0.000921662089984137</v>
       </c>
     </row>
     <row r="83">
@@ -4107,10 +4107,10 @@
         <v>93</v>
       </c>
       <c r="C83" t="n">
-        <v>0.00455103030531461</v>
+        <v>0.00463882513787856</v>
       </c>
       <c r="D83" t="n">
-        <v>0.001751310331722</v>
+        <v>0.00178170431859787</v>
       </c>
     </row>
     <row r="84">
@@ -4121,10 +4121,10 @@
         <v>57</v>
       </c>
       <c r="C84" t="n">
-        <v>0.00421457867119282</v>
+        <v>0.00429517931494125</v>
       </c>
       <c r="D84" t="n">
-        <v>0.000727124974454247</v>
+        <v>0.000740014434232476</v>
       </c>
     </row>
     <row r="85">
@@ -4135,7 +4135,7 @@
         <v>124</v>
       </c>
       <c r="C85" t="n">
-        <v>0.00393408699799003</v>
+        <v>0.00401047142210395</v>
       </c>
       <c r="D85"/>
     </row>
@@ -4147,7 +4147,7 @@
         <v>97</v>
       </c>
       <c r="C86" t="n">
-        <v>0.00298187230299212</v>
+        <v>0.00303855471955522</v>
       </c>
       <c r="D86"/>
     </row>
@@ -4159,10 +4159,10 @@
         <v>83</v>
       </c>
       <c r="C87" t="n">
-        <v>0.00277032330164156</v>
+        <v>0.00282297360488863</v>
       </c>
       <c r="D87" t="n">
-        <v>0.000303960274740397</v>
+        <v>0.000309940362173772</v>
       </c>
     </row>
     <row r="88">
@@ -4173,7 +4173,7 @@
         <v>74</v>
       </c>
       <c r="C88" t="n">
-        <v>0.00245881963555129</v>
+        <v>0.00250653946155477</v>
       </c>
       <c r="D88"/>
     </row>
@@ -4185,7 +4185,7 @@
         <v>73</v>
       </c>
       <c r="C89" t="n">
-        <v>0.00226208476203674</v>
+        <v>0.00230603452858629</v>
       </c>
       <c r="D89"/>
     </row>
@@ -4197,7 +4197,7 @@
         <v>90</v>
       </c>
       <c r="C90" t="n">
-        <v>0.00215932192471274</v>
+        <v>0.0021975191548252</v>
       </c>
       <c r="D90"/>
     </row>
@@ -4209,10 +4209,10 @@
         <v>47</v>
       </c>
       <c r="C91" t="n">
-        <v>0.00206005912858076</v>
+        <v>0.00209811575901352</v>
       </c>
       <c r="D91" t="n">
-        <v>0.000869957133691929</v>
+        <v>0.000884204008856405</v>
       </c>
     </row>
     <row r="92">
@@ -4223,10 +4223,10 @@
         <v>46</v>
       </c>
       <c r="C92" t="n">
-        <v>0.001882126801935</v>
+        <v>0.0019181127764312</v>
       </c>
       <c r="D92" t="n">
-        <v>0.000339048168231471</v>
+        <v>0.000345883039138015</v>
       </c>
     </row>
     <row r="93">
@@ -4237,7 +4237,7 @@
         <v>163</v>
       </c>
       <c r="C93" t="n">
-        <v>0.00186869641131444</v>
+        <v>0.00190498324456774</v>
       </c>
       <c r="D93"/>
     </row>
@@ -4249,7 +4249,7 @@
         <v>106</v>
       </c>
       <c r="C94" t="n">
-        <v>0.00186869641131444</v>
+        <v>0.00190498324456774</v>
       </c>
       <c r="D94"/>
     </row>
@@ -4261,7 +4261,7 @@
         <v>153</v>
       </c>
       <c r="C95" t="n">
-        <v>0.00176316609955953</v>
+        <v>0.00180123095018929</v>
       </c>
       <c r="D95"/>
     </row>
@@ -4273,10 +4273,10 @@
         <v>64</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0015092503205241</v>
+        <v>0.00153855747675692</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0000455267014720686</v>
+        <v>0.0000464199050722866</v>
       </c>
     </row>
     <row r="97">
@@ -4287,10 +4287,10 @@
         <v>131</v>
       </c>
       <c r="C97" t="n">
-        <v>0.00150208744552647</v>
+        <v>0.00153238618260028</v>
       </c>
       <c r="D97" t="n">
-        <v>0.000328759189391221</v>
+        <v>0.000334340464545882</v>
       </c>
     </row>
     <row r="98">
@@ -4301,7 +4301,7 @@
         <v>107</v>
       </c>
       <c r="C98" t="n">
-        <v>0.00137694062383486</v>
+        <v>0.00140365878502415</v>
       </c>
       <c r="D98"/>
     </row>
@@ -4313,7 +4313,7 @@
         <v>164</v>
       </c>
       <c r="C99" t="n">
-        <v>0.00137694062383486</v>
+        <v>0.00140365878502415</v>
       </c>
       <c r="D99"/>
     </row>
@@ -4325,7 +4325,7 @@
         <v>165</v>
       </c>
       <c r="C100" t="n">
-        <v>0.00103715174113462</v>
+        <v>0.00105955736318937</v>
       </c>
       <c r="D100"/>
     </row>
@@ -4337,7 +4337,7 @@
         <v>130</v>
       </c>
       <c r="C101" t="n">
-        <v>0.000726014358424912</v>
+        <v>0.000741673586999923</v>
       </c>
       <c r="D101"/>
     </row>
@@ -4349,7 +4349,7 @@
         <v>126</v>
       </c>
       <c r="C102" t="n">
-        <v>0.000688449962840732</v>
+        <v>0.000701829392512073</v>
       </c>
       <c r="D102"/>
     </row>
@@ -4361,7 +4361,7 @@
         <v>105</v>
       </c>
       <c r="C103" t="n">
-        <v>0.000616943307324584</v>
+        <v>0.000627856698795545</v>
       </c>
       <c r="D103"/>
     </row>
@@ -4373,7 +4373,7 @@
         <v>145</v>
       </c>
       <c r="C104" t="n">
-        <v>0.000518575870567309</v>
+        <v>0.000529778681594684</v>
       </c>
       <c r="D104"/>
     </row>
@@ -4385,7 +4385,7 @@
         <v>166</v>
       </c>
       <c r="C105" t="n">
-        <v>0.000393429048875701</v>
+        <v>0.000401051284018554</v>
       </c>
       <c r="D105"/>
     </row>
@@ -4397,7 +4397,7 @@
         <v>79</v>
       </c>
       <c r="C106" t="n">
-        <v>0.000196694175361153</v>
+        <v>0.000200504932968483</v>
       </c>
       <c r="D106"/>
     </row>
@@ -4434,10 +4434,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>16.3403695380059</v>
+        <v>16.3416618666596</v>
       </c>
       <c r="D2" t="n">
-        <v>0.364919314801013</v>
+        <v>0.364966200796807</v>
       </c>
     </row>
     <row r="3">
@@ -4448,10 +4448,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>6.51788880376076</v>
+        <v>6.51777469517085</v>
       </c>
       <c r="D3" t="n">
-        <v>0.148649506122588</v>
+        <v>0.149483132101543</v>
       </c>
     </row>
     <row r="4">
@@ -4462,10 +4462,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>6.22723903161778</v>
+        <v>6.22693384084823</v>
       </c>
       <c r="D4" t="n">
-        <v>0.137344309723072</v>
+        <v>0.137333677396879</v>
       </c>
     </row>
     <row r="5">
@@ -4476,10 +4476,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>5.78196952153187</v>
+        <v>5.78175384328398</v>
       </c>
       <c r="D5" t="n">
-        <v>0.173895046899155</v>
+        <v>0.173891851031029</v>
       </c>
     </row>
     <row r="6">
@@ -4490,10 +4490,10 @@
         <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75112364897646</v>
+        <v>4.75077424714615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.129801582746227</v>
+        <v>0.129793138447533</v>
       </c>
     </row>
     <row r="7">
@@ -4504,10 +4504,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.29688870687125</v>
+        <v>4.29551016526434</v>
       </c>
       <c r="D7" t="n">
-        <v>0.760395363004059</v>
+        <v>0.760088335441991</v>
       </c>
     </row>
     <row r="8">
@@ -4518,10 +4518,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>3.56531569965563</v>
+        <v>3.56579486530789</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0709566502638378</v>
+        <v>0.0709657729581015</v>
       </c>
     </row>
     <row r="9">
@@ -4532,10 +4532,10 @@
         <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>3.40976468453934</v>
+        <v>3.40983508152703</v>
       </c>
       <c r="D9" t="n">
-        <v>0.197089448395916</v>
+        <v>0.197090472795478</v>
       </c>
     </row>
     <row r="10">
@@ -4546,10 +4546,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>3.25289332287214</v>
+        <v>3.2527788563025</v>
       </c>
       <c r="D10" t="n">
-        <v>0.108663499471417</v>
+        <v>0.108659565304884</v>
       </c>
     </row>
     <row r="11">
@@ -4560,10 +4560,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>3.15596309415241</v>
+        <v>3.15587678225824</v>
       </c>
       <c r="D11" t="n">
-        <v>0.174451677946733</v>
+        <v>0.174437328289574</v>
       </c>
     </row>
     <row r="12">
@@ -4574,10 +4574,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>2.94775463378045</v>
+        <v>2.94806372159539</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0717211799235303</v>
+        <v>0.07173198581819</v>
       </c>
     </row>
     <row r="13">
@@ -4588,10 +4588,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>2.72620662807857</v>
+        <v>2.72609495261659</v>
       </c>
       <c r="D13" t="n">
-        <v>0.104650557514979</v>
+        <v>0.104642971896762</v>
       </c>
     </row>
     <row r="14">
@@ -4602,10 +4602,10 @@
         <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>2.65454340488704</v>
+        <v>2.65450884006315</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0501338485760552</v>
+        <v>0.0501332455260786</v>
       </c>
     </row>
     <row r="15">
@@ -4616,10 +4616,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>2.38729825062195</v>
+        <v>2.38739613161961</v>
       </c>
       <c r="D15" t="n">
-        <v>0.319167766070598</v>
+        <v>0.319182762232658</v>
       </c>
     </row>
     <row r="16">
@@ -4630,10 +4630,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>2.36803476006497</v>
+        <v>2.36796288589534</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0847669645851135</v>
+        <v>0.0847630239866693</v>
       </c>
     </row>
     <row r="17">
@@ -4644,10 +4644,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>2.26675503353507</v>
+        <v>2.26695125312262</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0418533205527473</v>
+        <v>0.0418574721223817</v>
       </c>
     </row>
     <row r="18">
@@ -4658,10 +4658,10 @@
         <v>53</v>
       </c>
       <c r="C18" t="n">
-        <v>2.16120215614226</v>
+        <v>2.16190915247882</v>
       </c>
       <c r="D18" t="n">
-        <v>0.630839632185262</v>
+        <v>0.631046876611651</v>
       </c>
     </row>
     <row r="19">
@@ -4672,10 +4672,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>1.78431039450407</v>
+        <v>1.78449052469228</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0132479013162543</v>
+        <v>0.0132512817326122</v>
       </c>
     </row>
     <row r="20">
@@ -4686,10 +4686,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="n">
-        <v>1.60443809805352</v>
+        <v>1.6045568246363</v>
       </c>
       <c r="D20" t="n">
-        <v>1.02470187994274</v>
+        <v>1.02480571441199</v>
       </c>
     </row>
     <row r="21">
@@ -4700,10 +4700,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>1.56894865858386</v>
+        <v>1.568986544644</v>
       </c>
       <c r="D21" t="n">
-        <v>0.158045752393243</v>
+        <v>0.158054034060133</v>
       </c>
     </row>
     <row r="22">
@@ -4714,10 +4714,10 @@
         <v>32</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3671290596746</v>
+        <v>1.36706008764098</v>
       </c>
       <c r="D22" t="n">
-        <v>0.024602274813773</v>
+        <v>0.0246008624733284</v>
       </c>
     </row>
     <row r="23">
@@ -4728,10 +4728,10 @@
         <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>1.30185458681485</v>
+        <v>1.30212288353511</v>
       </c>
       <c r="D23" t="n">
-        <v>0.12398872214353</v>
+        <v>0.124013734188933</v>
       </c>
     </row>
     <row r="24">
@@ -4742,10 +4742,10 @@
         <v>49</v>
       </c>
       <c r="C24" t="n">
-        <v>1.15782568183839</v>
+        <v>1.15781211665459</v>
       </c>
       <c r="D24" t="n">
-        <v>0.388147454124298</v>
+        <v>0.388147147303828</v>
       </c>
     </row>
     <row r="25">
@@ -4756,10 +4756,10 @@
         <v>55</v>
       </c>
       <c r="C25" t="n">
-        <v>1.10313487400028</v>
+        <v>1.1032148757848</v>
       </c>
       <c r="D25" t="n">
-        <v>0.091316681498599</v>
+        <v>0.091329827462734</v>
       </c>
     </row>
     <row r="26">
@@ -4770,10 +4770,10 @@
         <v>28</v>
       </c>
       <c r="C26" t="n">
-        <v>0.914810625981458</v>
+        <v>0.914748471908951</v>
       </c>
       <c r="D26" t="n">
-        <v>0.112719322261636</v>
+        <v>0.112713526040406</v>
       </c>
     </row>
     <row r="27">
@@ -4784,10 +4784,10 @@
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.86366333890105</v>
+        <v>0.86376269509832</v>
       </c>
       <c r="D27" t="n">
-        <v>0.131172557706573</v>
+        <v>0.131190806078947</v>
       </c>
     </row>
     <row r="28">
@@ -4798,10 +4798,10 @@
         <v>13</v>
       </c>
       <c r="C28" t="n">
-        <v>0.815602824465873</v>
+        <v>0.814399947104209</v>
       </c>
       <c r="D28" t="n">
-        <v>0.094353123616174</v>
+        <v>0.100056472702307</v>
       </c>
     </row>
     <row r="29">
@@ -4812,10 +4812,10 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>0.719770124787197</v>
+        <v>0.719736577546547</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0138090172437913</v>
+        <v>0.0138080383445599</v>
       </c>
     </row>
     <row r="30">
@@ -4826,10 +4826,10 @@
         <v>56</v>
       </c>
       <c r="C30" t="n">
-        <v>0.637769836102387</v>
+        <v>0.637767957096375</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0637842852856246</v>
+        <v>0.0637833909765124</v>
       </c>
     </row>
     <row r="31">
@@ -4840,10 +4840,10 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>0.630804205125401</v>
+        <v>0.630698100890269</v>
       </c>
       <c r="D31" t="n">
-        <v>0.21514285032078</v>
+        <v>0.215099761008479</v>
       </c>
     </row>
     <row r="32">
@@ -4854,10 +4854,10 @@
         <v>54</v>
       </c>
       <c r="C32" t="n">
-        <v>0.608494449146302</v>
+        <v>0.608625642131184</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0501820178937106</v>
+        <v>0.0501922784259376</v>
       </c>
     </row>
     <row r="33">
@@ -4868,10 +4868,10 @@
         <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>0.601069402914586</v>
+        <v>0.601109066988274</v>
       </c>
       <c r="D33" t="n">
-        <v>0.114916725818998</v>
+        <v>0.114931127079321</v>
       </c>
     </row>
     <row r="34">
@@ -4882,10 +4882,10 @@
         <v>75</v>
       </c>
       <c r="C34" t="n">
-        <v>0.564366858239162</v>
+        <v>0.564317099847651</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0274906116577773</v>
+        <v>0.0274888222439849</v>
       </c>
     </row>
     <row r="35">
@@ -4896,10 +4896,10 @@
         <v>89</v>
       </c>
       <c r="C35" t="n">
-        <v>0.55395138987645</v>
+        <v>0.553986634179406</v>
       </c>
       <c r="D35" t="n">
-        <v>0.017223332453407</v>
+        <v>0.0172252220198623</v>
       </c>
     </row>
     <row r="36">
@@ -4910,10 +4910,10 @@
         <v>44</v>
       </c>
       <c r="C36" t="n">
-        <v>0.53364988089015</v>
+        <v>0.533610796502323</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0672478275891398</v>
+        <v>0.0672437902588174</v>
       </c>
     </row>
     <row r="37">
@@ -4924,10 +4924,10 @@
         <v>81</v>
       </c>
       <c r="C37" t="n">
-        <v>0.406629786645901</v>
+        <v>0.406617206121492</v>
       </c>
       <c r="D37" t="n">
-        <v>0.17598432539977</v>
+        <v>0.175977369525517</v>
       </c>
     </row>
     <row r="38">
@@ -4938,10 +4938,10 @@
         <v>29</v>
       </c>
       <c r="C38" t="n">
-        <v>0.393257124299549</v>
+        <v>0.393317167573086</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0144218386698097</v>
+        <v>0.0144237310221212</v>
       </c>
     </row>
     <row r="39">
@@ -4952,10 +4952,10 @@
         <v>107</v>
       </c>
       <c r="C39" t="n">
-        <v>0.376478799111195</v>
+        <v>0.376460428719311</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0569277071811371</v>
+        <v>0.0569255066041069</v>
       </c>
     </row>
     <row r="40">
@@ -4966,10 +4966,10 @@
         <v>88</v>
       </c>
       <c r="C40" t="n">
-        <v>0.375992656868376</v>
+        <v>0.376090634527935</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0119771154406029</v>
+        <v>0.0119805882665518</v>
       </c>
     </row>
     <row r="41">
@@ -4980,10 +4980,10 @@
         <v>27</v>
       </c>
       <c r="C41" t="n">
-        <v>0.319907100323329</v>
+        <v>0.319966284722752</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0792373807900135</v>
+        <v>0.0792516795713162</v>
       </c>
     </row>
     <row r="42">
@@ -4994,10 +4994,10 @@
         <v>61</v>
       </c>
       <c r="C42" t="n">
-        <v>0.311547220728577</v>
+        <v>0.311533277594606</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0172972008546067</v>
+        <v>0.017295263988654</v>
       </c>
     </row>
     <row r="43">
@@ -5008,10 +5008,10 @@
         <v>41</v>
       </c>
       <c r="C43" t="n">
-        <v>0.286951946092299</v>
+        <v>0.287017555621548</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0167429224293851</v>
+        <v>0.0167476611580681</v>
       </c>
     </row>
     <row r="44">
@@ -5022,10 +5022,10 @@
         <v>87</v>
       </c>
       <c r="C44" t="n">
-        <v>0.257536867560212</v>
+        <v>0.257546713674983</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00630636905983868</v>
+        <v>0.00630700331476103</v>
       </c>
     </row>
     <row r="45">
@@ -5036,10 +5036,10 @@
         <v>69</v>
       </c>
       <c r="C45" t="n">
-        <v>0.250044031462655</v>
+        <v>0.250047245262464</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0225874571938306</v>
+        <v>0.022589536277193</v>
       </c>
     </row>
     <row r="46">
@@ -5050,10 +5050,10 @@
         <v>106</v>
       </c>
       <c r="C46" t="n">
-        <v>0.240955188548261</v>
+        <v>0.240932634902632</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0196478778738606</v>
+        <v>0.019645659674528</v>
       </c>
     </row>
     <row r="47">
@@ -5064,10 +5064,10 @@
         <v>114</v>
       </c>
       <c r="C47" t="n">
-        <v>0.236651365549334</v>
+        <v>0.236621238972088</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0245403392704892</v>
+        <v>0.0245344346007489</v>
       </c>
     </row>
     <row r="48">
@@ -5078,10 +5078,10 @@
         <v>82</v>
       </c>
       <c r="C48" t="n">
-        <v>0.234992180800151</v>
+        <v>0.235017760704586</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00760673412748419</v>
+        <v>0.00760762449770051</v>
       </c>
     </row>
     <row r="49">
@@ -5092,10 +5092,10 @@
         <v>64</v>
       </c>
       <c r="C49" t="n">
-        <v>0.230585283865868</v>
+        <v>0.230564123421666</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0509844526870072</v>
+        <v>0.0509783767753283</v>
       </c>
     </row>
     <row r="50">
@@ -5106,10 +5106,10 @@
         <v>38</v>
       </c>
       <c r="C50" t="n">
-        <v>0.219742906044752</v>
+        <v>0.21975122573986</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00600844586702114</v>
+        <v>0.0060086872243454</v>
       </c>
     </row>
     <row r="51">
@@ -5120,10 +5120,10 @@
         <v>46</v>
       </c>
       <c r="C51" t="n">
-        <v>0.180419394007164</v>
+        <v>0.18040569029904</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0166865917056073</v>
+        <v>0.0166850776816214</v>
       </c>
     </row>
     <row r="52">
@@ -5134,10 +5134,10 @@
         <v>162</v>
       </c>
       <c r="C52" t="n">
-        <v>0.180274979366738</v>
+        <v>0.180255950866786</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0482170531919115</v>
+        <v>0.048211338126906</v>
       </c>
     </row>
     <row r="53">
@@ -5148,10 +5148,10 @@
         <v>43</v>
       </c>
       <c r="C53" t="n">
-        <v>0.175302426010932</v>
+        <v>0.175282668877571</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0704758478739547</v>
+        <v>0.0704671562035202</v>
       </c>
     </row>
     <row r="54">
@@ -5162,10 +5162,10 @@
         <v>83</v>
       </c>
       <c r="C54" t="n">
-        <v>0.168522161421196</v>
+        <v>0.168502071930805</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0229008601942342</v>
+        <v>0.0228979232440653</v>
       </c>
     </row>
     <row r="55">
@@ -5176,10 +5176,10 @@
         <v>22</v>
       </c>
       <c r="C55" t="n">
-        <v>0.161638211676001</v>
+        <v>0.161676597587428</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0265707855618042</v>
+        <v>0.0265770666322205</v>
       </c>
     </row>
     <row r="56">
@@ -5190,10 +5190,10 @@
         <v>72</v>
       </c>
       <c r="C56" t="n">
-        <v>0.159943909553694</v>
+        <v>0.15995203921521</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00568762009029767</v>
+        <v>0.00568780060194871</v>
       </c>
     </row>
     <row r="57">
@@ -5204,10 +5204,10 @@
         <v>131</v>
       </c>
       <c r="C57" t="n">
-        <v>0.159462823768081</v>
+        <v>0.15945461104189</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0288106145615336</v>
+        <v>0.0288087319627314</v>
       </c>
     </row>
     <row r="58">
@@ -5218,10 +5218,10 @@
         <v>76</v>
       </c>
       <c r="C58" t="n">
-        <v>0.158651012341907</v>
+        <v>0.158673366659809</v>
       </c>
       <c r="D58" t="n">
-        <v>0.045737570407468</v>
+        <v>0.0457539772131932</v>
       </c>
     </row>
     <row r="59">
@@ -5232,10 +5232,10 @@
         <v>36</v>
       </c>
       <c r="C59" t="n">
-        <v>0.140466714222925</v>
+        <v>0.14047524908631</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00788768201295411</v>
+        <v>0.00788783623797873</v>
       </c>
     </row>
     <row r="60">
@@ -5246,10 +5246,10 @@
         <v>31</v>
       </c>
       <c r="C60" t="n">
-        <v>0.137410891541032</v>
+        <v>0.137395260037261</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0449355261351212</v>
+        <v>0.0449289816918205</v>
       </c>
     </row>
     <row r="61">
@@ -5260,10 +5260,10 @@
         <v>45</v>
       </c>
       <c r="C61" t="n">
-        <v>0.135808327999466</v>
+        <v>0.135806111433529</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0204445409249088</v>
+        <v>0.0204457783616086</v>
       </c>
     </row>
     <row r="62">
@@ -5274,10 +5274,10 @@
         <v>80</v>
       </c>
       <c r="C62" t="n">
-        <v>0.110803758156809</v>
+        <v>0.110803736305645</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00364327926675692</v>
+        <v>0.00364336006938954</v>
       </c>
     </row>
     <row r="63">
@@ -5288,10 +5288,10 @@
         <v>98</v>
       </c>
       <c r="C63" t="n">
-        <v>0.096861716502859</v>
+        <v>0.0968590850529563</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0098797210525114</v>
+        <v>0.00987867127821817</v>
       </c>
     </row>
     <row r="64">
@@ -5302,10 +5302,10 @@
         <v>47</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0957017874459538</v>
+        <v>0.0957086574341561</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0295079921162402</v>
+        <v>0.0295107728838257</v>
       </c>
     </row>
     <row r="65">
@@ -5316,10 +5316,10 @@
         <v>33</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0882387344369958</v>
+        <v>0.0882681183753547</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0214519495552798</v>
+        <v>0.0214593103647159</v>
       </c>
     </row>
     <row r="66">
@@ -5330,10 +5330,10 @@
         <v>60</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0854309559855238</v>
+        <v>0.0854199033065721</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0133012523857728</v>
+        <v>0.0132973407545517</v>
       </c>
     </row>
     <row r="67">
@@ -5344,10 +5344,10 @@
         <v>26</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0812239280245435</v>
+        <v>0.0812389184245935</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0116606661657457</v>
+        <v>0.0116625794027242</v>
       </c>
     </row>
     <row r="68">
@@ -5358,7 +5358,7 @@
         <v>52</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0735733971407114</v>
+        <v>0.0735541085857273</v>
       </c>
       <c r="D68"/>
     </row>
@@ -5370,10 +5370,10 @@
         <v>97</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0692411801897809</v>
+        <v>0.0692410464152097</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0243421446622777</v>
+        <v>0.0243414152156006</v>
       </c>
     </row>
     <row r="70">
@@ -5384,10 +5384,10 @@
         <v>74</v>
       </c>
       <c r="C70" t="n">
-        <v>0.067218041652683</v>
+        <v>0.0672108440905825</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00668684478327204</v>
+        <v>0.00668616124790953</v>
       </c>
     </row>
     <row r="71">
@@ -5398,7 +5398,7 @@
         <v>39</v>
       </c>
       <c r="C71" t="n">
-        <v>0.06156481136528</v>
+        <v>0.0615545147950379</v>
       </c>
       <c r="D71"/>
     </row>
@@ -5410,10 +5410,10 @@
         <v>92</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0575685432085077</v>
+        <v>0.0575790883844144</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00404441216473035</v>
+        <v>0.00404498640104643</v>
       </c>
     </row>
     <row r="73">
@@ -5424,10 +5424,10 @@
         <v>103</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0558564601377837</v>
+        <v>0.0558554742148481</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0072784081124607</v>
+        <v>0.00727819198305638</v>
       </c>
     </row>
     <row r="74">
@@ -5438,10 +5438,10 @@
         <v>57</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0444333676544535</v>
+        <v>0.044441119444064</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0027361000168165</v>
+        <v>0.00273663123169244</v>
       </c>
     </row>
     <row r="75">
@@ -5452,10 +5452,10 @@
         <v>123</v>
       </c>
       <c r="C75" t="n">
-        <v>0.041275304519162</v>
+        <v>0.0412794290949981</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0080909810456354</v>
+        <v>0.00809159300126105</v>
       </c>
     </row>
     <row r="76">
@@ -5466,10 +5466,10 @@
         <v>117</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0412210726264895</v>
+        <v>0.0412218327332593</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00275171881252815</v>
+        <v>0.0027513876411545</v>
       </c>
     </row>
     <row r="77">
@@ -5480,10 +5480,10 @@
         <v>116</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0394546465321653</v>
+        <v>0.0394545630763963</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0048306054789954</v>
+        <v>0.00483024384608776</v>
       </c>
     </row>
     <row r="78">
@@ -5494,10 +5494,10 @@
         <v>105</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0379787166826076</v>
+        <v>0.0379799407001521</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00304539560801592</v>
+        <v>0.00304531061956671</v>
       </c>
     </row>
     <row r="79">
@@ -5508,10 +5508,10 @@
         <v>140</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0360922136210034</v>
+        <v>0.0360885361652888</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00329405287532919</v>
+        <v>0.00329315460379549</v>
       </c>
     </row>
     <row r="80">
@@ -5522,10 +5522,10 @@
         <v>158</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0357424290263582</v>
+        <v>0.0357480677974404</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00168638120545988</v>
+        <v>0.00168680940639728</v>
       </c>
     </row>
     <row r="81">
@@ -5536,10 +5536,10 @@
         <v>85</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0351413218389282</v>
+        <v>0.035147110580455</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00223147331606697</v>
+        <v>0.00223192621137626</v>
       </c>
     </row>
     <row r="82">
@@ -5550,10 +5550,10 @@
         <v>71</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0326582679579259</v>
+        <v>0.0326619136604909</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00209412826448036</v>
+        <v>0.00209457650402667</v>
       </c>
     </row>
     <row r="83">
@@ -5564,7 +5564,7 @@
         <v>99</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0316309736631204</v>
+        <v>0.0316297890797849</v>
       </c>
       <c r="D83"/>
     </row>
@@ -5576,10 +5576,10 @@
         <v>139</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0313758170533332</v>
+        <v>0.0313841297664091</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00523947935992204</v>
+        <v>0.00524152469478577</v>
       </c>
     </row>
     <row r="85">
@@ -5590,10 +5590,10 @@
         <v>91</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0298202618941446</v>
+        <v>0.0298250290235258</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00668946759658577</v>
+        <v>0.00669114910307872</v>
       </c>
     </row>
     <row r="86">
@@ -5604,10 +5604,10 @@
         <v>160</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0297184103989921</v>
+        <v>0.0297134464866567</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0166486551989316</v>
+        <v>0.0166461770143964</v>
       </c>
     </row>
     <row r="87">
@@ -5618,10 +5618,10 @@
         <v>95</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0295457685029536</v>
+        <v>0.0295461004520193</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00598291523636964</v>
+        <v>0.00598137732196592</v>
       </c>
     </row>
     <row r="88">
@@ -5632,10 +5632,10 @@
         <v>102</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0294915921757449</v>
+        <v>0.0294900037062563</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00836889204896852</v>
+        <v>0.00836874621831844</v>
       </c>
     </row>
     <row r="89">
@@ -5646,7 +5646,7 @@
         <v>90</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0289973929406735</v>
+        <v>0.028990242796974</v>
       </c>
       <c r="D89"/>
     </row>
@@ -5658,10 +5658,10 @@
         <v>78</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0256712998428392</v>
+        <v>0.0256698708611311</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0038681151108631</v>
+        <v>0.00386771393409036</v>
       </c>
     </row>
     <row r="91">
@@ -5672,10 +5672,10 @@
         <v>96</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0256615203212098</v>
+        <v>0.0256641501038899</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00664478539283624</v>
+        <v>0.00664577834495545</v>
       </c>
     </row>
     <row r="92">
@@ -5686,10 +5686,10 @@
         <v>68</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0216161878598986</v>
+        <v>0.0216140206011366</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00500467422972252</v>
+        <v>0.00500333103498446</v>
       </c>
     </row>
     <row r="93">
@@ -5700,10 +5700,10 @@
         <v>73</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0206172319516331</v>
+        <v>0.0206166093532046</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00906946714473541</v>
+        <v>0.0090693907818614</v>
       </c>
     </row>
     <row r="94">
@@ -5714,10 +5714,10 @@
         <v>143</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0197244616446968</v>
+        <v>0.0197225605249409</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00670892909133827</v>
+        <v>0.0067068795102041</v>
       </c>
     </row>
     <row r="95">
@@ -5728,10 +5728,10 @@
         <v>147</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0194367992385843</v>
+        <v>0.0194313573189654</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0134471690570031</v>
+        <v>0.0134430571653996</v>
       </c>
     </row>
     <row r="96">
@@ -5742,10 +5742,10 @@
         <v>168</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0191004059207158</v>
+        <v>0.0190963875430284</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0127808770907428</v>
+        <v>0.0127783505917011</v>
       </c>
     </row>
     <row r="97">
@@ -5756,10 +5756,10 @@
         <v>115</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0186067067748186</v>
+        <v>0.0186067906975823</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00246551259817442</v>
+        <v>0.00246572573655409</v>
       </c>
     </row>
     <row r="98">
@@ -5770,10 +5770,10 @@
         <v>62</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0183543284382216</v>
+        <v>0.0183576322802629</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00293734422480663</v>
+        <v>0.00293824038624759</v>
       </c>
     </row>
     <row r="99">
@@ -5784,10 +5784,10 @@
         <v>70</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0178994139860595</v>
+        <v>0.0179009714449529</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00235547475936501</v>
+        <v>0.00235512932184248</v>
       </c>
     </row>
     <row r="100">
@@ -5798,10 +5798,10 @@
         <v>169</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0176228646727078</v>
+        <v>0.0176228204521005</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00507237707616203</v>
+        <v>0.00507194153967515</v>
       </c>
     </row>
     <row r="101">
@@ -5812,10 +5812,10 @@
         <v>138</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0165665652057967</v>
+        <v>0.016564924693143</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00185358351927208</v>
+        <v>0.00185341504255475</v>
       </c>
     </row>
     <row r="102">
@@ -5826,10 +5826,10 @@
         <v>108</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0163720305170195</v>
+        <v>0.0163773060721655</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0106598070644074</v>
+        <v>0.0106630716517072</v>
       </c>
     </row>
     <row r="103">
@@ -5840,10 +5840,10 @@
         <v>93</v>
       </c>
       <c r="C103" t="n">
-        <v>0.016284070387818</v>
+        <v>0.0162848852949877</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00229361056036175</v>
+        <v>0.00229383266052794</v>
       </c>
     </row>
     <row r="104">
@@ -5854,10 +5854,10 @@
         <v>77</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0149113256045441</v>
+        <v>0.0149099596104707</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00273498055236116</v>
+        <v>0.00273402095514348</v>
       </c>
     </row>
     <row r="105">
@@ -5868,10 +5868,10 @@
         <v>86</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0140552285037183</v>
+        <v>0.0140572890748737</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00201327935472589</v>
+        <v>0.0020135781075336</v>
       </c>
     </row>
     <row r="106">
@@ -5882,10 +5882,10 @@
         <v>112</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0114864371120666</v>
+        <v>0.0114842257669918</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00438291868901427</v>
+        <v>0.00438250764268453</v>
       </c>
     </row>
     <row r="107">
@@ -5896,10 +5896,10 @@
         <v>58</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00994805168119341</v>
+        <v>0.00995011862370593</v>
       </c>
       <c r="D107" t="n">
-        <v>0.000865244098210358</v>
+        <v>0.000865407396954317</v>
       </c>
     </row>
     <row r="108">
@@ -5910,10 +5910,10 @@
         <v>79</v>
       </c>
       <c r="C108" t="n">
-        <v>0.00946857729403005</v>
+        <v>0.00946940839145006</v>
       </c>
       <c r="D108" t="n">
-        <v>0.000598209856622833</v>
+        <v>0.000598048541075432</v>
       </c>
     </row>
     <row r="109">
@@ -5924,7 +5924,7 @@
         <v>170</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00861631421020671</v>
+        <v>0.00861351645857161</v>
       </c>
       <c r="D109"/>
     </row>
@@ -5936,10 +5936,10 @@
         <v>100</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00781217081803749</v>
+        <v>0.00781499872210221</v>
       </c>
       <c r="D110" t="n">
-        <v>0.000517222988787047</v>
+        <v>0.000518019480477547</v>
       </c>
     </row>
     <row r="111">
@@ -5950,7 +5950,7 @@
         <v>155</v>
       </c>
       <c r="C111" t="n">
-        <v>0.00779227838199572</v>
+        <v>0.00779161582114557</v>
       </c>
       <c r="D111"/>
     </row>
@@ -5962,7 +5962,7 @@
         <v>164</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0077399357150925</v>
+        <v>0.00773785181134503</v>
       </c>
       <c r="D112"/>
     </row>
@@ -5974,10 +5974,10 @@
         <v>104</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00773643509087286</v>
+        <v>0.00773685206736114</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00132693872080473</v>
+        <v>0.00132690765332156</v>
       </c>
     </row>
     <row r="114">
@@ -5988,10 +5988,10 @@
         <v>50</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00764347406992903</v>
+        <v>0.00764209855422093</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00492737014416636</v>
+        <v>0.00492660482862357</v>
       </c>
     </row>
     <row r="115">
@@ -6002,7 +6002,7 @@
         <v>171</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00654644511804976</v>
+        <v>0.00654815647051074</v>
       </c>
       <c r="D115"/>
     </row>
@@ -6014,10 +6014,10 @@
         <v>113</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00617037805902535</v>
+        <v>0.00616903133528503</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00362955849553183</v>
+        <v>0.00362821786694141</v>
       </c>
     </row>
     <row r="117">
@@ -6028,7 +6028,7 @@
         <v>51</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00591344335439638</v>
+        <v>0.00591442986738659</v>
       </c>
       <c r="D117"/>
     </row>
@@ -6040,10 +6040,10 @@
         <v>126</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00558355119579296</v>
+        <v>0.00558395893937707</v>
       </c>
       <c r="D118" t="n">
-        <v>0.00115410349329897</v>
+        <v>0.00115438021349579</v>
       </c>
     </row>
     <row r="119">
@@ -6054,7 +6054,7 @@
         <v>94</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00543441349094345</v>
+        <v>0.00543327530447121</v>
       </c>
       <c r="D119"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>122</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00539629558277401</v>
+        <v>0.00539634031839956</v>
       </c>
       <c r="D120" t="n">
-        <v>0.00123235214220535</v>
+        <v>0.00123234364749038</v>
       </c>
     </row>
     <row r="121">
@@ -6080,7 +6080,7 @@
         <v>130</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00483597344577606</v>
+        <v>0.00483387324479411</v>
       </c>
       <c r="D121"/>
     </row>
@@ -6092,10 +6092,10 @@
         <v>109</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0034267777182468</v>
+        <v>0.00342706683545743</v>
       </c>
       <c r="D122" t="n">
-        <v>0.000356041595137824</v>
+        <v>0.000356207481303227</v>
       </c>
     </row>
     <row r="123">
@@ -6106,7 +6106,7 @@
         <v>163</v>
       </c>
       <c r="C123" t="n">
-        <v>0.00311466650806061</v>
+        <v>0.00311398034450118</v>
       </c>
       <c r="D123"/>
     </row>
@@ -6118,7 +6118,7 @@
         <v>101</v>
       </c>
       <c r="C124" t="n">
-        <v>0.00275271307684238</v>
+        <v>0.00275229518766117</v>
       </c>
       <c r="D124"/>
     </row>
@@ -6130,10 +6130,10 @@
         <v>136</v>
       </c>
       <c r="C125" t="n">
-        <v>0.00266553086413415</v>
+        <v>0.00266576179172187</v>
       </c>
       <c r="D125" t="n">
-        <v>0.000251896828010007</v>
+        <v>0.000251605887793505</v>
       </c>
     </row>
     <row r="126">
@@ -6144,10 +6144,10 @@
         <v>132</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0025260615499865</v>
+        <v>0.00252568655131178</v>
       </c>
       <c r="D126" t="n">
-        <v>0.000212051995630788</v>
+        <v>0.000211449346693792</v>
       </c>
     </row>
     <row r="127">
@@ -6158,7 +6158,7 @@
         <v>48</v>
       </c>
       <c r="C127" t="n">
-        <v>0.00231958028649142</v>
+        <v>0.00231857292264834</v>
       </c>
       <c r="D127"/>
     </row>
@@ -6170,7 +6170,7 @@
         <v>144</v>
       </c>
       <c r="C128" t="n">
-        <v>0.00227296086236</v>
+        <v>0.00227236253405944</v>
       </c>
       <c r="D128"/>
     </row>
@@ -6182,7 +6182,7 @@
         <v>142</v>
       </c>
       <c r="C129" t="n">
-        <v>0.00188394705026929</v>
+        <v>0.0018831288763299</v>
       </c>
       <c r="D129"/>
     </row>
@@ -6194,7 +6194,7 @@
         <v>172</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0014965446366289</v>
+        <v>0.00149683890921961</v>
       </c>
       <c r="D130"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>128</v>
       </c>
       <c r="C131" t="n">
-        <v>0.00148515371654911</v>
+        <v>0.0014857306427319</v>
       </c>
       <c r="D131" t="n">
-        <v>0.000138327611613312</v>
+        <v>0.00013819619213571</v>
       </c>
     </row>
     <row r="132">
@@ -6220,7 +6220,7 @@
         <v>173</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0014532035748619</v>
+        <v>0.00145329450458777</v>
       </c>
       <c r="D132"/>
     </row>
@@ -6232,10 +6232,10 @@
         <v>153</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0013258475318235</v>
+        <v>0.00132621593596831</v>
       </c>
       <c r="D133" t="n">
-        <v>0.000595529386284204</v>
+        <v>0.000595938407639598</v>
       </c>
     </row>
     <row r="134">
@@ -6246,7 +6246,7 @@
         <v>145</v>
       </c>
       <c r="C134" t="n">
-        <v>0.00131995759266029</v>
+        <v>0.00131999530673519</v>
       </c>
       <c r="D134"/>
     </row>
@@ -6258,10 +6258,10 @@
         <v>154</v>
       </c>
       <c r="C135" t="n">
-        <v>0.00128045054789576</v>
+        <v>0.00128144962202281</v>
       </c>
       <c r="D135" t="n">
-        <v>0.000133274109538564</v>
+        <v>0.00013329477761492</v>
       </c>
     </row>
     <row r="136">
@@ -6272,7 +6272,7 @@
         <v>165</v>
       </c>
       <c r="C136" t="n">
-        <v>0.00123255311809684</v>
+        <v>0.00123373961745808</v>
       </c>
       <c r="D136"/>
     </row>
@@ -6284,10 +6284,10 @@
         <v>42</v>
       </c>
       <c r="C137" t="n">
-        <v>0.00112481168378119</v>
+        <v>0.00112432319255408</v>
       </c>
       <c r="D137" t="n">
-        <v>0.000128351294167125</v>
+        <v>0.000128295552853185</v>
       </c>
     </row>
     <row r="138">
@@ -6298,7 +6298,7 @@
         <v>119</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00103740720921775</v>
+        <v>0.00103790087927966</v>
       </c>
       <c r="D138"/>
     </row>
@@ -6310,7 +6310,7 @@
         <v>161</v>
       </c>
       <c r="C139" t="n">
-        <v>0.000922997919245635</v>
+        <v>0.000922597073137179</v>
       </c>
       <c r="D139"/>
     </row>
@@ -6322,10 +6322,10 @@
         <v>174</v>
       </c>
       <c r="C140" t="n">
-        <v>0.000919275033170778</v>
+        <v>0.000919209051858425</v>
       </c>
       <c r="D140" t="n">
-        <v>0.000204861794556036</v>
+        <v>0.000204537183800384</v>
       </c>
     </row>
     <row r="141">
@@ -6336,10 +6336,10 @@
         <v>30</v>
       </c>
       <c r="C141" t="n">
-        <v>0.000907717416699578</v>
+        <v>0.000908211868035587</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0000917045317402739</v>
+        <v>0.0000917432529488665</v>
       </c>
     </row>
     <row r="142">
@@ -6350,7 +6350,7 @@
         <v>175</v>
       </c>
       <c r="C142" t="n">
-        <v>0.000839983116322694</v>
+        <v>0.000839618322473947</v>
       </c>
       <c r="D142"/>
     </row>
@@ -6362,7 +6362,7 @@
         <v>127</v>
       </c>
       <c r="C143" t="n">
-        <v>0.000820479638527545</v>
+        <v>0.000820123314788007</v>
       </c>
       <c r="D143"/>
     </row>
@@ -6374,10 +6374,10 @@
         <v>176</v>
       </c>
       <c r="C144" t="n">
-        <v>0.00065094940846202</v>
+        <v>0.000651444288172053</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0000151269257583571</v>
+        <v>0.0000151989036349364</v>
       </c>
     </row>
     <row r="145">
@@ -6388,7 +6388,7 @@
         <v>177</v>
       </c>
       <c r="C145" t="n">
-        <v>0.000560266571534148</v>
+        <v>0.000560800833632297</v>
       </c>
       <c r="D145"/>
     </row>
@@ -6400,7 +6400,7 @@
         <v>178</v>
       </c>
       <c r="C146" t="n">
-        <v>0.000470972871201373</v>
+        <v>0.000470768333749366</v>
       </c>
       <c r="D146"/>
     </row>
@@ -6412,7 +6412,7 @@
         <v>179</v>
       </c>
       <c r="C147" t="n">
-        <v>0.000389013812090704</v>
+        <v>0.000389233657729537</v>
       </c>
       <c r="D147"/>
     </row>
@@ -6424,7 +6424,7 @@
         <v>129</v>
       </c>
       <c r="C148" t="n">
-        <v>0.00033617105601325</v>
+        <v>0.000336469391912891</v>
       </c>
       <c r="D148"/>
     </row>
